--- a/developer-di-practitioner/10-mod3-excel-writer/files/template.xlsx
+++ b/developer-di-practitioner/10-mod3-excel-writer/files/template.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Sales Chart" sheetId="4" r:id="rId1"/>
     <sheet name="SourceData" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="179017" concurrentCalc="0"/>
+  <calcPr fullCalcOnLoad="1" calcId="179017" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="http://schemas.microsoft.com/office/mac/excel/2008/main">
       <mx:ArchID Flags="2"/>
@@ -2992,11 +2992,11 @@
         <v>2</v>
       </c>
       <c r="B10" s="6">
-        <f>SUM(B5,B8)</f>
+        <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
       <c r="C10" s="6">
-        <f t="shared" ref="C10:G10" si="4">SUM(C5,C8)</f>
+        <f t="shared" ref="C10:G10" si="4">SUM(C5:C8)</f>
         <v>0</v>
       </c>
       <c r="D10" s="6">

--- a/developer-di-practitioner/10-mod3-excel-writer/files/template.xlsx
+++ b/developer-di-practitioner/10-mod3-excel-writer/files/template.xlsx
@@ -112,7 +112,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00&quot;€&quot;"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="yyyy"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
@@ -394,7 +394,7 @@
             <c:numRef>
               <c:f>SourceData!$B$5:$G$5</c:f>
               <c:numCache>
-                <c:formatCode>#,##0.00"€"</c:formatCode>
+                <c:formatCode>"$"#,##0.00</c:formatCode>
                 <c:ptCount val="6"/>
               </c:numCache>
             </c:numRef>
@@ -474,7 +474,7 @@
             <c:numRef>
               <c:f>SourceData!$B$6:$G$6</c:f>
               <c:numCache>
-                <c:formatCode>#,##0.00"€"</c:formatCode>
+                <c:formatCode>"$"#,##0.00</c:formatCode>
                 <c:ptCount val="6"/>
               </c:numCache>
             </c:numRef>
@@ -554,7 +554,7 @@
             <c:numRef>
               <c:f>SourceData!$B$7:$G$7</c:f>
               <c:numCache>
-                <c:formatCode>#,##0.00"€"</c:formatCode>
+                <c:formatCode>"$"#,##0.00</c:formatCode>
                 <c:ptCount val="6"/>
               </c:numCache>
             </c:numRef>
@@ -641,7 +641,7 @@
             <c:numRef>
               <c:f>SourceData!$B$8:$G$8</c:f>
               <c:numCache>
-                <c:formatCode>#,##0.00"€"</c:formatCode>
+                <c:formatCode>"$"#,##0.00</c:formatCode>
                 <c:ptCount val="6"/>
               </c:numCache>
             </c:numRef>
@@ -798,7 +798,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="#,##0.00&quot;€&quot;" sourceLinked="1"/>
+        <c:numFmt formatCode="&quot;$&quot;#,##0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1207,7 +1207,7 @@
             <c:numRef>
               <c:f>SourceData!$H$5:$H$8</c:f>
               <c:numCache>
-                <c:formatCode>#,##0.00"€"</c:formatCode>
+                <c:formatCode>"$"#,##0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -2785,7 +2785,7 @@
     <col min="3" max="3" width="12.7109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="4" max="7" width="12.28515625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="8" max="8" width="19.85546875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="10.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="12.28515625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="10" max="10" width="11.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="11" max="11" width="11.85546875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="12" max="16384" width="9.140625" style="1" collapsed="1"/>
